--- a/Year 12A Grades 2.xlsx
+++ b/Year 12A Grades 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebube\Documents\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C98C807A-BE38-453D-B9C5-DA79565BEE41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D7D29E1-B698-47C6-951F-092D4B37C3A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{3206C89B-315C-403E-A44F-EEBE8FF4250D}"/>
   </bookViews>
@@ -249,7 +249,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -266,25 +266,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -541,64 +551,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>76</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>97</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>79</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>74</c:v>
+                  <c:v>69</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>70</c:v>
+                  <c:v>92</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>49</c:v>
                 </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>62</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>58</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="18">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>33</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>85</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>70</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -708,64 +718,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>98</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>74</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>79</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>43</c:v>
+                  <c:v>83</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>54</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>90</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>76</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>33</c:v>
+                  <c:v>94</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>82</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>65</c:v>
+                  <c:v>83</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>34</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>58</c:v>
+                  <c:v>74</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>34</c:v>
+                  <c:v>71</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>65</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>25</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>24</c:v>
                 </c:pt>
-                <c:pt idx="16">
-                  <c:v>46</c:v>
-                </c:pt>
                 <c:pt idx="17">
-                  <c:v>65</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>86</c:v>
+                  <c:v>91</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>17</c:v>
+                  <c:v>92</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -875,64 +885,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>94</c:v>
+                  <c:v>57</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>55</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>21</c:v>
+                  <c:v>77</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>30</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>73</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>95</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>54</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>86</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>77</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
                 <c:pt idx="15">
-                  <c:v>38</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2</c:v>
+                  <c:v>76</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>8</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5</c:v>
+                  <c:v>98</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1042,64 +1052,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>15</c:v>
+                  <c:v>69</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>73</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>18</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>90</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>30</c:v>
+                  <c:v>97</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>89</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>77</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>51</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>28</c:v>
+                  <c:v>95</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>97</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>78</c:v>
+                  <c:v>86</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>84</c:v>
+                  <c:v>86</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>70</c:v>
+                  <c:v>71</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>59</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>17</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>84</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>57</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>54</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>68</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>41</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1227,64 +1237,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>70.75</c:v>
+                  <c:v>37.25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38.25</c:v>
+                  <c:v>52.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>53.75</c:v>
+                  <c:v>50.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>78</c:v>
+                  <c:v>53</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>39.75</c:v>
+                  <c:v>57.75</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>52.25</c:v>
+                  <c:v>31.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>54.75</c:v>
+                  <c:v>69.25</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>41.25</c:v>
+                  <c:v>41.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>53.5</c:v>
+                  <c:v>58.25</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>69.5</c:v>
+                  <c:v>55</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>30.5</c:v>
+                  <c:v>57.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>60.75</c:v>
+                  <c:v>68.75</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>52</c:v>
+                  <c:v>57</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>58.5</c:v>
+                  <c:v>21.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>31.75</c:v>
+                  <c:v>41.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>51.5</c:v>
+                  <c:v>43.25</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>41.5</c:v>
+                  <c:v>49.25</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>55</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>51.75</c:v>
+                  <c:v>67.25</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>33.25</c:v>
+                  <c:v>80.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1667,64 +1677,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>20</c:v>
+                  <c:v>69</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>69</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>40</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>77</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>44</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>54</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>94</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>65</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>96</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>72</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>83</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>71</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>100</c:v>
-                </c:pt>
                 <c:pt idx="19">
-                  <c:v>31</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2075,64 +2085,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>8</c:v>
+                  <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>95</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>82</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>96</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>97</c:v>
-                </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="12">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>90</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>46</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>97</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>33</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>54</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>73</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>40</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2242,64 +2252,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>62</c:v>
+                  <c:v>53</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>55</c:v>
+                  <c:v>69</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38</c:v>
+                  <c:v>87</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>13</c:v>
+                  <c:v>83</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>23</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>84</c:v>
+                  <c:v>92</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>86</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>54</c:v>
+                  <c:v>94</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>65</c:v>
+                  <c:v>82</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>86</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>15</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>24</c:v>
+                  <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>85</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>52</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>91</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>100</c:v>
+                  <c:v>93</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>52</c:v>
+                  <c:v>92</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2409,64 +2419,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>38</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>55</c:v>
-                </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>51</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>63</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>76</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>97</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>46</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1</c:v>
-                </c:pt>
                 <c:pt idx="19">
-                  <c:v>41</c:v>
+                  <c:v>57</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2576,64 +2586,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>50</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>51</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>75</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>45</c:v>
-                </c:pt>
                 <c:pt idx="7">
-                  <c:v>46</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>87</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>91</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>61</c:v>
-                </c:pt>
                 <c:pt idx="15">
-                  <c:v>17</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>35</c:v>
+                  <c:v>87</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>43</c:v>
+                  <c:v>76</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>35</c:v>
+                  <c:v>53</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>21</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2761,64 +2771,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>30.5</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>47.25</c:v>
+                  <c:v>54.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>43.5</c:v>
+                  <c:v>47.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>34.25</c:v>
+                  <c:v>68.25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>50.5</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>40</c:v>
+                  <c:v>60.25</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>73.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>58.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>64.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>40.25</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>74.25</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>34.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>48.75</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>33.25</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>72</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>76.25</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>62.5</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>60.5</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>46.5</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>29.25</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>15.25</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>44.25</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>51.5</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>47.75</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>52.25</c:v>
-                </c:pt>
                 <c:pt idx="19">
-                  <c:v>38.5</c:v>
+                  <c:v>63.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3201,64 +3211,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>8</c:v>
+                  <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>95</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>82</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>96</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>97</c:v>
-                </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="12">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>90</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>46</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>97</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>33</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>54</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>73</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>40</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3584,64 +3594,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>62</c:v>
+                  <c:v>53</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>55</c:v>
+                  <c:v>69</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38</c:v>
+                  <c:v>87</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>13</c:v>
+                  <c:v>83</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>23</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>84</c:v>
+                  <c:v>92</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>86</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>54</c:v>
+                  <c:v>94</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>65</c:v>
+                  <c:v>82</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>86</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>15</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>24</c:v>
+                  <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>85</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>52</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>91</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>100</c:v>
+                  <c:v>93</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>52</c:v>
+                  <c:v>92</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3992,64 +4002,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>38</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>55</c:v>
-                </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>51</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>63</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>76</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>97</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>46</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1</c:v>
-                </c:pt>
                 <c:pt idx="19">
-                  <c:v>41</c:v>
+                  <c:v>57</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4399,64 +4409,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>50</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>51</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>75</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>45</c:v>
-                </c:pt>
                 <c:pt idx="7">
-                  <c:v>46</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>87</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>91</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>61</c:v>
-                </c:pt>
                 <c:pt idx="15">
-                  <c:v>17</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>35</c:v>
+                  <c:v>87</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>43</c:v>
+                  <c:v>76</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>35</c:v>
+                  <c:v>53</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>21</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4807,64 +4817,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>76</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>97</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>79</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>74</c:v>
+                  <c:v>69</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>70</c:v>
+                  <c:v>92</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>49</c:v>
                 </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>62</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>58</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="18">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>33</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>85</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>70</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5190,64 +5200,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>98</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>74</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>79</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>43</c:v>
+                  <c:v>83</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>54</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>90</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>76</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>33</c:v>
+                  <c:v>94</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>82</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>65</c:v>
+                  <c:v>83</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>34</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>58</c:v>
+                  <c:v>74</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>34</c:v>
+                  <c:v>71</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>65</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>25</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>24</c:v>
                 </c:pt>
-                <c:pt idx="16">
-                  <c:v>46</c:v>
-                </c:pt>
                 <c:pt idx="17">
-                  <c:v>65</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>86</c:v>
+                  <c:v>91</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>17</c:v>
+                  <c:v>92</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5598,64 +5608,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>94</c:v>
+                  <c:v>57</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>55</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>21</c:v>
+                  <c:v>77</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>30</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>73</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>95</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>54</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>86</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>77</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
                 <c:pt idx="15">
-                  <c:v>38</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2</c:v>
+                  <c:v>76</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>8</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5</c:v>
+                  <c:v>98</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6005,64 +6015,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>15</c:v>
+                  <c:v>69</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>73</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>18</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>90</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>30</c:v>
+                  <c:v>97</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>89</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>77</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>51</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>28</c:v>
+                  <c:v>95</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>97</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>78</c:v>
+                  <c:v>86</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>84</c:v>
+                  <c:v>86</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>70</c:v>
+                  <c:v>71</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>59</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>17</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>84</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>57</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>54</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>68</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>41</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6413,64 +6423,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>55</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>92</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>21</c:v>
+                  <c:v>97</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>55</c:v>
+                  <c:v>81</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>20</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20</c:v>
+                  <c:v>86</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4</c:v>
+                  <c:v>99</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>79</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>62</c:v>
+                  <c:v>78</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>29</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>9</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>74</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>64</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>98</c:v>
+                  <c:v>78</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>56</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>96</c:v>
+                  <c:v>61</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>30</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>6</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>20</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6580,64 +6590,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>55</c:v>
+                  <c:v>82</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>86</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>37</c:v>
+                  <c:v>98</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>41</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>28</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>36</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>80</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>85</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2</c:v>
+                  <c:v>76</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>18</c:v>
+                  <c:v>62</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>37</c:v>
+                  <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>81</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>18</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>21</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>73</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>17</c:v>
+                  <c:v>92</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>44</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>15</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>76</c:v>
+                  <c:v>84</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6747,64 +6757,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>27</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>54</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>60</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>35</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>18</c:v>
+                  <c:v>93</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>35</c:v>
+                  <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>38</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>90</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>78</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>54</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>16</c:v>
-                </c:pt>
                 <c:pt idx="15">
-                  <c:v>64</c:v>
+                  <c:v>77</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>23</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>90</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>91</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>79</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6914,64 +6924,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>20</c:v>
+                  <c:v>69</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>69</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>40</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>77</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>44</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>54</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>94</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>65</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>96</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>72</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>83</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>71</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>100</c:v>
-                </c:pt>
                 <c:pt idx="19">
-                  <c:v>31</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7099,64 +7109,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>39.25</c:v>
+                  <c:v>64.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>49.75</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>49.5</c:v>
+                  <c:v>72.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>26</c:v>
+                  <c:v>43.75</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>42.25</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>47.75</c:v>
+                  <c:v>33.75</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>32.25</c:v>
+                  <c:v>61</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>50.25</c:v>
+                  <c:v>64.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>40.75</c:v>
+                  <c:v>76.25</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>41.5</c:v>
+                  <c:v>60.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>57</c:v>
+                  <c:v>34.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>54.5</c:v>
+                  <c:v>41.75</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>68.5</c:v>
+                  <c:v>21.25</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>54.5</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>51.75</c:v>
+                  <c:v>60.75</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>69</c:v>
+                  <c:v>31.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>51.75</c:v>
+                  <c:v>61</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>48.5</c:v>
+                  <c:v>38.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>53</c:v>
+                  <c:v>34.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>51.5</c:v>
+                  <c:v>55.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7539,64 +7549,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>55</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>92</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>21</c:v>
+                  <c:v>97</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>55</c:v>
+                  <c:v>81</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>20</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20</c:v>
+                  <c:v>86</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4</c:v>
+                  <c:v>99</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>79</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>62</c:v>
+                  <c:v>78</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>29</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>9</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>74</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>64</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>98</c:v>
+                  <c:v>78</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>56</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>96</c:v>
+                  <c:v>61</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>30</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>6</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>20</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7922,64 +7932,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>55</c:v>
+                  <c:v>82</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>86</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>37</c:v>
+                  <c:v>98</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>41</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>28</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>36</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>80</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>85</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2</c:v>
+                  <c:v>76</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>18</c:v>
+                  <c:v>62</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>37</c:v>
+                  <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>81</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>18</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>21</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>73</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>17</c:v>
+                  <c:v>92</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>44</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>15</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>76</c:v>
+                  <c:v>84</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8330,64 +8340,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>27</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>54</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>60</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>35</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>18</c:v>
+                  <c:v>93</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>35</c:v>
+                  <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>38</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>90</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>78</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>54</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>16</c:v>
-                </c:pt>
                 <c:pt idx="15">
-                  <c:v>64</c:v>
+                  <c:v>77</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>23</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>90</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>91</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>79</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -19449,7 +19459,7 @@
       <calculatedColumnFormula>AVERAGE(B5:E5)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -19879,29 +19889,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="47.5" x14ac:dyDescent="1.1000000000000001">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="5"/>
+      <c r="B1" s="4"/>
     </row>
     <row r="2" spans="1:2" ht="31" x14ac:dyDescent="0.7">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="6"/>
+      <c r="B2" s="5"/>
     </row>
     <row r="4" spans="1:2" ht="26" x14ac:dyDescent="0.6">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="26" x14ac:dyDescent="0.6">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="26" x14ac:dyDescent="0.6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>38</v>
       </c>
     </row>
@@ -19933,47 +19943,47 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -20004,27 +20014,27 @@
       </c>
       <c r="B5">
         <f ca="1">RANDBETWEEN(0,100)</f>
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:E20" ca="1" si="0">RANDBETWEEN(0,100)</f>
-        <v>98</v>
+        <v>17</v>
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="E5">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="F5">
         <f ca="1">AVERAGE(B5:E5)</f>
-        <v>70.75</v>
+        <v>37.25</v>
       </c>
       <c r="G5" t="str">
         <f ca="1">IF(F5 &lt;50,"Fail", "Pass")</f>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -20033,15 +20043,15 @@
       </c>
       <c r="B6">
         <f t="shared" ref="B6:E24" ca="1" si="1">RANDBETWEEN(0,100)</f>
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="0"/>
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="E6">
         <f t="shared" ca="1" si="0"/>
@@ -20049,11 +20059,11 @@
       </c>
       <c r="F6">
         <f t="shared" ref="F6:F24" ca="1" si="2">AVERAGE(B6:E6)</f>
-        <v>38.25</v>
+        <v>52.5</v>
       </c>
       <c r="G6" t="str">
         <f t="shared" ref="G6:G24" ca="1" si="3">IF(F6 &lt;50,"Fail", "Pass")</f>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -20062,23 +20072,23 @@
       </c>
       <c r="B7">
         <f t="shared" ca="1" si="1"/>
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="0"/>
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="E7">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F7">
         <f t="shared" ca="1" si="2"/>
-        <v>53.75</v>
+        <v>50.5</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -20091,23 +20101,23 @@
       </c>
       <c r="B8">
         <f t="shared" ca="1" si="1"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="0"/>
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="E8">
         <f t="shared" ca="1" si="0"/>
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="F8">
         <f t="shared" ca="1" si="2"/>
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="G8" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -20120,27 +20130,27 @@
       </c>
       <c r="B9">
         <f t="shared" ca="1" si="1"/>
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="0"/>
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="E9">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="F9">
         <f t="shared" ca="1" si="2"/>
-        <v>39.75</v>
+        <v>57.75</v>
       </c>
       <c r="G9" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.35">
@@ -20149,27 +20159,27 @@
       </c>
       <c r="B10">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="0"/>
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <f t="shared" ca="1" si="0"/>
-        <v>89</v>
+        <v>19</v>
       </c>
       <c r="F10">
         <f t="shared" ca="1" si="2"/>
-        <v>52.25</v>
+        <v>31.5</v>
       </c>
       <c r="G10" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
@@ -20178,7 +20188,7 @@
       </c>
       <c r="B11">
         <f t="shared" ca="1" si="1"/>
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="0"/>
@@ -20186,15 +20196,15 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E11">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="F11">
         <f t="shared" ca="1" si="2"/>
-        <v>54.75</v>
+        <v>69.25</v>
       </c>
       <c r="G11" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -20207,23 +20217,23 @@
       </c>
       <c r="B12">
         <f t="shared" ca="1" si="1"/>
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="0"/>
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E12">
         <f t="shared" ca="1" si="0"/>
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="F12">
         <f t="shared" ca="1" si="2"/>
-        <v>41.25</v>
+        <v>41.5</v>
       </c>
       <c r="G12" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -20236,23 +20246,23 @@
       </c>
       <c r="B13">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="0"/>
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="E13">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="F13">
         <f t="shared" ca="1" si="2"/>
-        <v>53.5</v>
+        <v>58.25</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -20265,23 +20275,23 @@
       </c>
       <c r="B14">
         <f t="shared" ca="1" si="1"/>
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="0"/>
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E14">
         <f t="shared" ca="1" si="0"/>
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="F14">
         <f t="shared" ca="1" si="2"/>
-        <v>69.5</v>
+        <v>55</v>
       </c>
       <c r="G14" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -20294,27 +20304,27 @@
       </c>
       <c r="B15">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="0"/>
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="E15">
         <f t="shared" ca="1" si="0"/>
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F15">
         <f t="shared" ca="1" si="2"/>
-        <v>30.5</v>
+        <v>57.5</v>
       </c>
       <c r="G15" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
@@ -20323,23 +20333,23 @@
       </c>
       <c r="B16">
         <f t="shared" ca="1" si="1"/>
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="0"/>
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E16">
         <f t="shared" ca="1" si="0"/>
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F16">
         <f t="shared" ca="1" si="2"/>
-        <v>60.75</v>
+        <v>68.75</v>
       </c>
       <c r="G16" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -20352,23 +20362,23 @@
       </c>
       <c r="B17">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="0"/>
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E17">
         <f t="shared" ca="1" si="0"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F17">
         <f t="shared" ca="1" si="2"/>
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G17" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -20381,27 +20391,27 @@
       </c>
       <c r="B18">
         <f t="shared" ca="1" si="1"/>
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="0"/>
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="E18">
         <f t="shared" ca="1" si="0"/>
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="F18">
         <f t="shared" ca="1" si="2"/>
-        <v>58.5</v>
+        <v>21.5</v>
       </c>
       <c r="G18" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -20410,23 +20420,23 @@
       </c>
       <c r="B19">
         <f t="shared" ca="1" si="1"/>
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="E19">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F19">
         <f t="shared" ca="1" si="2"/>
-        <v>31.75</v>
+        <v>41.5</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -20439,27 +20449,27 @@
       </c>
       <c r="B20">
         <f t="shared" ca="1" si="1"/>
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E20">
         <f t="shared" ca="1" si="0"/>
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="F20">
         <f t="shared" ca="1" si="2"/>
-        <v>51.5</v>
+        <v>43.25</v>
       </c>
       <c r="G20" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -20468,23 +20478,23 @@
       </c>
       <c r="B21">
         <f t="shared" ca="1" si="1"/>
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="1"/>
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="E21">
         <f t="shared" ca="1" si="1"/>
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="F21">
         <f t="shared" ca="1" si="2"/>
-        <v>41.5</v>
+        <v>49.25</v>
       </c>
       <c r="G21" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -20497,27 +20507,27 @@
       </c>
       <c r="B22">
         <f t="shared" ca="1" si="1"/>
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="1"/>
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="D22">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="E22">
         <f t="shared" ca="1" si="1"/>
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F22">
         <f t="shared" ca="1" si="2"/>
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="G22" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -20526,23 +20536,23 @@
       </c>
       <c r="B23">
         <f t="shared" ca="1" si="1"/>
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="1"/>
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D23">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="E23">
         <f t="shared" ca="1" si="1"/>
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="F23">
         <f t="shared" ca="1" si="2"/>
-        <v>51.75</v>
+        <v>67.25</v>
       </c>
       <c r="G23" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -20555,27 +20565,27 @@
       </c>
       <c r="B24">
         <f t="shared" ca="1" si="1"/>
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="D24">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="E24">
         <f t="shared" ca="1" si="1"/>
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="F24">
         <f t="shared" ca="1" si="2"/>
-        <v>33.25</v>
+        <v>80.75</v>
       </c>
       <c r="G24" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -20584,19 +20594,19 @@
       </c>
       <c r="B26">
         <f ca="1">AVERAGE(B5:B24)</f>
-        <v>52.6</v>
+        <v>49.2</v>
       </c>
       <c r="C26">
         <f t="shared" ref="C26:E26" ca="1" si="4">AVERAGE(C5:C24)</f>
-        <v>57.4</v>
+        <v>50</v>
       </c>
       <c r="D26">
         <f t="shared" ca="1" si="4"/>
-        <v>38.5</v>
+        <v>52.25</v>
       </c>
       <c r="E26">
         <f t="shared" ca="1" si="4"/>
-        <v>55.15</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
@@ -20605,11 +20615,11 @@
       </c>
       <c r="B27">
         <f ca="1">MIN(B5:B24)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C27">
         <f t="shared" ref="C27:E27" ca="1" si="5">MIN(C5:C24)</f>
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D27">
         <f t="shared" ca="1" si="5"/>
@@ -20617,7 +20627,7 @@
       </c>
       <c r="E27">
         <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
@@ -20626,19 +20636,19 @@
       </c>
       <c r="B28">
         <f ca="1">MAX(B5:B24)</f>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C28">
         <f t="shared" ref="C28:E28" ca="1" si="6">MAX(C5:C24)</f>
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D28">
         <f t="shared" ca="1" si="6"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E28">
         <f t="shared" ca="1" si="6"/>
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -20676,47 +20686,47 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -20737,7 +20747,7 @@
       <c r="F4" t="s">
         <v>28</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="3" t="s">
         <v>30</v>
       </c>
     </row>
@@ -20747,27 +20757,27 @@
       </c>
       <c r="B5">
         <f ca="1">RANDBETWEEN(0,100)</f>
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:E20" ca="1" si="0">RANDBETWEEN(0,100)</f>
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="E5">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="F5">
         <f ca="1">AVERAGE(B5:E5)</f>
-        <v>39.25</v>
+        <v>64.5</v>
       </c>
       <c r="G5" t="str">
         <f ca="1">IF(F5 &lt;50,"Fail", "Pass")</f>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -20776,23 +20786,23 @@
       </c>
       <c r="B6">
         <f t="shared" ref="B6:E24" ca="1" si="1">RANDBETWEEN(0,100)</f>
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E6">
         <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="F6">
         <f t="shared" ref="F6:F24" ca="1" si="2">AVERAGE(B6:E6)</f>
-        <v>49.75</v>
+        <v>37</v>
       </c>
       <c r="G6" t="str">
         <f t="shared" ref="G6:G24" ca="1" si="3">IF(F6 &lt;50,"Fail", "Pass")</f>
@@ -20805,27 +20815,27 @@
       </c>
       <c r="B7">
         <f t="shared" ca="1" si="1"/>
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="0"/>
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E7">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="F7">
         <f t="shared" ca="1" si="2"/>
-        <v>49.5</v>
+        <v>72.75</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.35">
@@ -20834,23 +20844,23 @@
       </c>
       <c r="B8">
         <f t="shared" ca="1" si="1"/>
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="E8">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="F8">
         <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <v>43.75</v>
       </c>
       <c r="G8" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -20863,23 +20873,23 @@
       </c>
       <c r="B9">
         <f t="shared" ca="1" si="1"/>
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="E9">
         <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F9">
         <f t="shared" ca="1" si="2"/>
-        <v>42.25</v>
+        <v>38</v>
       </c>
       <c r="G9" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -20892,23 +20902,23 @@
       </c>
       <c r="B10">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E10">
         <f t="shared" ca="1" si="0"/>
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="F10">
         <f t="shared" ca="1" si="2"/>
-        <v>47.75</v>
+        <v>33.75</v>
       </c>
       <c r="G10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -20921,27 +20931,27 @@
       </c>
       <c r="B11">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="0"/>
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="E11">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="F11">
         <f t="shared" ca="1" si="2"/>
-        <v>32.25</v>
+        <v>61</v>
       </c>
       <c r="G11" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.35">
@@ -20950,23 +20960,23 @@
       </c>
       <c r="B12">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="0"/>
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="E12">
         <f t="shared" ca="1" si="0"/>
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="F12">
         <f t="shared" ca="1" si="2"/>
-        <v>50.25</v>
+        <v>64.5</v>
       </c>
       <c r="G12" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -20979,27 +20989,27 @@
       </c>
       <c r="B13">
         <f t="shared" ca="1" si="1"/>
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="E13">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F13">
         <f t="shared" ca="1" si="2"/>
-        <v>40.75</v>
+        <v>76.25</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
@@ -21008,27 +21018,27 @@
       </c>
       <c r="B14">
         <f t="shared" ca="1" si="1"/>
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="E14">
         <f t="shared" ca="1" si="0"/>
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F14">
         <f t="shared" ca="1" si="2"/>
-        <v>41.5</v>
+        <v>60.5</v>
       </c>
       <c r="G14" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.35">
@@ -21037,27 +21047,27 @@
       </c>
       <c r="B15">
         <f t="shared" ca="1" si="1"/>
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="E15">
         <f t="shared" ca="1" si="0"/>
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="F15">
         <f t="shared" ca="1" si="2"/>
-        <v>57</v>
+        <v>34.5</v>
       </c>
       <c r="G15" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
@@ -21066,27 +21076,27 @@
       </c>
       <c r="B16">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="0"/>
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="E16">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="F16">
         <f t="shared" ca="1" si="2"/>
-        <v>54.5</v>
+        <v>41.75</v>
       </c>
       <c r="G16" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -21095,27 +21105,27 @@
       </c>
       <c r="B17">
         <f t="shared" ca="1" si="1"/>
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="0"/>
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="E17">
         <f t="shared" ca="1" si="0"/>
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="F17">
         <f t="shared" ca="1" si="2"/>
-        <v>68.5</v>
+        <v>21.25</v>
       </c>
       <c r="G17" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -21124,27 +21134,27 @@
       </c>
       <c r="B18">
         <f t="shared" ca="1" si="1"/>
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E18">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="F18">
         <f t="shared" ca="1" si="2"/>
-        <v>54.5</v>
+        <v>38</v>
       </c>
       <c r="G18" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -21153,23 +21163,23 @@
       </c>
       <c r="B19">
         <f t="shared" ca="1" si="1"/>
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E19">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F19">
         <f t="shared" ca="1" si="2"/>
-        <v>51.75</v>
+        <v>60.75</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -21182,27 +21192,27 @@
       </c>
       <c r="B20">
         <f t="shared" ca="1" si="1"/>
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="0"/>
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="E20">
         <f t="shared" ca="1" si="0"/>
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="F20">
         <f t="shared" ca="1" si="2"/>
-        <v>69</v>
+        <v>31.5</v>
       </c>
       <c r="G20" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -21211,23 +21221,23 @@
       </c>
       <c r="B21">
         <f t="shared" ca="1" si="1"/>
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="E21">
         <f t="shared" ca="1" si="1"/>
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="F21">
         <f t="shared" ca="1" si="2"/>
-        <v>51.75</v>
+        <v>61</v>
       </c>
       <c r="G21" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -21240,23 +21250,23 @@
       </c>
       <c r="B22">
         <f t="shared" ca="1" si="1"/>
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="1"/>
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D22">
         <f t="shared" ca="1" si="1"/>
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="E22">
         <f t="shared" ca="1" si="1"/>
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="F22">
         <f t="shared" ca="1" si="2"/>
-        <v>48.5</v>
+        <v>38.5</v>
       </c>
       <c r="G22" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -21269,27 +21279,27 @@
       </c>
       <c r="B23">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D23">
         <f t="shared" ca="1" si="1"/>
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="E23">
         <f t="shared" ca="1" si="1"/>
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="F23">
         <f t="shared" ca="1" si="2"/>
-        <v>53</v>
+        <v>34.5</v>
       </c>
       <c r="G23" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
@@ -21298,23 +21308,23 @@
       </c>
       <c r="B24">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="1"/>
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D24">
         <f t="shared" ca="1" si="1"/>
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="E24">
         <f t="shared" ca="1" si="1"/>
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F24">
         <f t="shared" ca="1" si="2"/>
-        <v>51.5</v>
+        <v>55.5</v>
       </c>
       <c r="G24" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -21327,19 +21337,19 @@
       </c>
       <c r="B26">
         <f ca="1">AVERAGE(B5:B24)</f>
-        <v>46.4</v>
+        <v>55.25</v>
       </c>
       <c r="C26">
         <f t="shared" ref="C26:E26" ca="1" si="4">AVERAGE(C5:C24)</f>
-        <v>42.75</v>
+        <v>48.8</v>
       </c>
       <c r="D26">
         <f t="shared" ca="1" si="4"/>
-        <v>47.25</v>
+        <v>46.4</v>
       </c>
       <c r="E26">
         <f t="shared" ca="1" si="4"/>
-        <v>59.45</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
@@ -21348,19 +21358,19 @@
       </c>
       <c r="B27">
         <f ca="1">MIN(B5:B24)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C27">
         <f t="shared" ref="C27:E27" ca="1" si="5">MIN(C5:C24)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D27">
         <f t="shared" ca="1" si="5"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E27">
         <f t="shared" ca="1" si="5"/>
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
@@ -21369,19 +21379,19 @@
       </c>
       <c r="B28">
         <f ca="1">MAX(B5:B24)</f>
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C28">
         <f t="shared" ref="C28:E28" ca="1" si="6">MAX(C5:C24)</f>
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="D28">
         <f t="shared" ca="1" si="6"/>
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E28">
         <f t="shared" ca="1" si="6"/>
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -21419,47 +21429,47 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -21490,23 +21500,23 @@
       </c>
       <c r="B5">
         <f ca="1">RANDBETWEEN(0,100)</f>
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:E20" ca="1" si="0">RANDBETWEEN(0,100)</f>
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F5">
         <f ca="1">AVERAGE(B5:E5)</f>
-        <v>30.5</v>
+        <v>41</v>
       </c>
       <c r="G5" t="str">
         <f ca="1">IF(F5 &lt;50,"Fail", "Pass")</f>
@@ -21519,27 +21529,27 @@
       </c>
       <c r="B6">
         <f t="shared" ref="B6:E24" ca="1" si="1">RANDBETWEEN(0,100)</f>
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="0"/>
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="E6">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F6">
         <f t="shared" ref="F6:F24" ca="1" si="2">AVERAGE(B6:E6)</f>
-        <v>47.25</v>
+        <v>54.5</v>
       </c>
       <c r="G6" t="str">
         <f t="shared" ref="G6:G24" ca="1" si="3">IF(F6 &lt;50,"Fail", "Pass")</f>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -21548,23 +21558,23 @@
       </c>
       <c r="B7">
         <f t="shared" ca="1" si="1"/>
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="0"/>
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="E7">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F7">
         <f t="shared" ca="1" si="2"/>
-        <v>43.5</v>
+        <v>47.75</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -21577,27 +21587,27 @@
       </c>
       <c r="B8">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E8">
         <f t="shared" ca="1" si="0"/>
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="F8">
         <f t="shared" ca="1" si="2"/>
-        <v>34.25</v>
+        <v>68.25</v>
       </c>
       <c r="G8" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.35">
@@ -21606,23 +21616,23 @@
       </c>
       <c r="B9">
         <f t="shared" ca="1" si="1"/>
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="E9">
         <f t="shared" ca="1" si="0"/>
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F9">
         <f t="shared" ca="1" si="2"/>
-        <v>50.5</v>
+        <v>80</v>
       </c>
       <c r="G9" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -21635,27 +21645,27 @@
       </c>
       <c r="B10">
         <f t="shared" ca="1" si="1"/>
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="E10">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="F10">
         <f t="shared" ca="1" si="2"/>
-        <v>40</v>
+        <v>60.25</v>
       </c>
       <c r="G10" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
@@ -21664,23 +21674,23 @@
       </c>
       <c r="B11">
         <f t="shared" ca="1" si="1"/>
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="0"/>
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E11">
         <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F11">
         <f t="shared" ca="1" si="2"/>
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G11" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -21693,27 +21703,27 @@
       </c>
       <c r="B12">
         <f t="shared" ca="1" si="1"/>
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="E12">
         <f t="shared" ca="1" si="0"/>
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="F12">
         <f t="shared" ca="1" si="2"/>
-        <v>76.25</v>
+        <v>36.5</v>
       </c>
       <c r="G12" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.35">
@@ -21722,23 +21732,23 @@
       </c>
       <c r="B13">
         <f t="shared" ca="1" si="1"/>
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="0"/>
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="E13">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>87</v>
       </c>
       <c r="F13">
         <f t="shared" ca="1" si="2"/>
-        <v>62.5</v>
+        <v>73.5</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -21751,23 +21761,23 @@
       </c>
       <c r="B14">
         <f t="shared" ca="1" si="1"/>
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="0"/>
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="E14">
         <f t="shared" ca="1" si="0"/>
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F14">
         <f t="shared" ca="1" si="2"/>
-        <v>60.5</v>
+        <v>58.5</v>
       </c>
       <c r="G14" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -21780,23 +21790,23 @@
       </c>
       <c r="B15">
         <f t="shared" ca="1" si="1"/>
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="F15">
         <f t="shared" ca="1" si="2"/>
-        <v>28</v>
+        <v>46.5</v>
       </c>
       <c r="G15" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -21809,27 +21819,27 @@
       </c>
       <c r="B16">
         <f t="shared" ca="1" si="1"/>
-        <v>37</v>
+        <v>95</v>
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="E16">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="F16">
         <f t="shared" ca="1" si="2"/>
-        <v>46.5</v>
+        <v>60</v>
       </c>
       <c r="G16" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -21838,7 +21848,7 @@
       </c>
       <c r="B17">
         <f t="shared" ca="1" si="1"/>
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="0"/>
@@ -21846,19 +21856,19 @@
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="E17">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="F17">
         <f t="shared" ca="1" si="2"/>
-        <v>29.25</v>
+        <v>64.5</v>
       </c>
       <c r="G17" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -21867,23 +21877,23 @@
       </c>
       <c r="B18">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="E18">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="F18">
         <f t="shared" ca="1" si="2"/>
-        <v>15.25</v>
+        <v>40.25</v>
       </c>
       <c r="G18" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -21896,27 +21906,27 @@
       </c>
       <c r="B19">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E19">
         <f t="shared" ca="1" si="0"/>
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="F19">
         <f t="shared" ca="1" si="2"/>
-        <v>45</v>
+        <v>74.25</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -21925,23 +21935,23 @@
       </c>
       <c r="B20">
         <f t="shared" ca="1" si="1"/>
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="0"/>
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="E20">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F20">
         <f t="shared" ca="1" si="2"/>
-        <v>44.25</v>
+        <v>34.5</v>
       </c>
       <c r="G20" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -21954,27 +21964,27 @@
       </c>
       <c r="B21">
         <f t="shared" ca="1" si="1"/>
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="1"/>
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="1"/>
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="E21">
         <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="F21">
         <f t="shared" ca="1" si="2"/>
-        <v>51.5</v>
+        <v>48.75</v>
       </c>
       <c r="G21" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -21983,23 +21993,23 @@
       </c>
       <c r="B22">
         <f t="shared" ca="1" si="1"/>
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="1"/>
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="D22">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E22">
         <f t="shared" ca="1" si="1"/>
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="F22">
         <f t="shared" ca="1" si="2"/>
-        <v>47.75</v>
+        <v>33.25</v>
       </c>
       <c r="G22" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -22012,23 +22022,23 @@
       </c>
       <c r="B23">
         <f t="shared" ca="1" si="1"/>
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="1"/>
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D23">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="E23">
         <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="F23">
         <f t="shared" ca="1" si="2"/>
-        <v>52.25</v>
+        <v>72</v>
       </c>
       <c r="G23" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -22041,27 +22051,27 @@
       </c>
       <c r="B24">
         <f t="shared" ca="1" si="1"/>
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="1"/>
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="D24">
         <f t="shared" ca="1" si="1"/>
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E24">
         <f t="shared" ca="1" si="1"/>
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F24">
         <f t="shared" ca="1" si="2"/>
-        <v>38.5</v>
+        <v>63.25</v>
       </c>
       <c r="G24" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -22070,19 +22080,19 @@
       </c>
       <c r="B26">
         <f ca="1">AVERAGE(B5:B24)</f>
-        <v>58.45</v>
+        <v>58.3</v>
       </c>
       <c r="C26">
         <f t="shared" ref="C26:E26" ca="1" si="4">AVERAGE(C5:C24)</f>
-        <v>50.6</v>
+        <v>57.25</v>
       </c>
       <c r="D26">
         <f t="shared" ca="1" si="4"/>
-        <v>40.85</v>
+        <v>52.55</v>
       </c>
       <c r="E26">
         <f t="shared" ca="1" si="4"/>
-        <v>33.200000000000003</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
@@ -22091,19 +22101,19 @@
       </c>
       <c r="B27">
         <f ca="1">MIN(B5:B24)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C27">
         <f t="shared" ref="C27:E27" ca="1" si="5">MIN(C5:C24)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D27">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
@@ -22112,15 +22122,15 @@
       </c>
       <c r="B28">
         <f ca="1">MAX(B5:B24)</f>
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C28">
         <f t="shared" ref="C28:E28" ca="1" si="6">MAX(C5:C24)</f>
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D28">
         <f t="shared" ca="1" si="6"/>
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E28">
         <f t="shared" ca="1" si="6"/>
